--- a/output/Jiangxi/上饶市_news.xlsx
+++ b/output/Jiangxi/上饶市_news.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="60">
   <si>
     <t>location</t>
   </si>
@@ -98,7 +98,7 @@
     <t/>
   </si>
   <si>
-    <t>True</t>
+    <t>False</t>
   </si>
   <si>
     <t>[]</t>
@@ -235,18 +235,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -704,28 +704,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -849,15 +849,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1206,57 +1203,54 @@
   <sheetPr/>
   <dimension ref="A1:P12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="10" max="10" width="9" style="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1288,20 +1282,20 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>23</v>
       </c>
       <c r="K2" t="s">
         <v>24</v>
       </c>
       <c r="L2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M2">
         <v>3</v>
       </c>
-      <c r="N2">
-        <v>0</v>
+      <c r="N2" t="s">
+        <v>22</v>
       </c>
       <c r="O2" t="s">
         <v>25</v>
@@ -1338,20 +1332,20 @@
       <c r="I3">
         <v>2</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" t="s">
         <v>23</v>
       </c>
       <c r="K3" t="s">
         <v>24</v>
       </c>
       <c r="L3">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M3">
         <v>10</v>
       </c>
-      <c r="N3">
-        <v>0</v>
+      <c r="N3" t="s">
+        <v>22</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
@@ -1388,20 +1382,20 @@
       <c r="I4">
         <v>2</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" t="s">
         <v>23</v>
       </c>
       <c r="K4" t="s">
         <v>24</v>
       </c>
       <c r="L4">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M4">
         <v>9</v>
       </c>
-      <c r="N4">
-        <v>0</v>
+      <c r="N4" t="s">
+        <v>22</v>
       </c>
       <c r="O4" t="s">
         <v>31</v>
@@ -1438,20 +1432,20 @@
       <c r="I5">
         <v>7877</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" t="s">
         <v>23</v>
       </c>
       <c r="K5" t="s">
         <v>24</v>
       </c>
       <c r="L5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
-      <c r="N5">
-        <v>0</v>
+      <c r="N5" t="s">
+        <v>22</v>
       </c>
       <c r="O5" t="s">
         <v>34</v>
@@ -1488,20 +1482,20 @@
       <c r="I6">
         <v>22347</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" t="s">
         <v>23</v>
       </c>
       <c r="K6" t="s">
         <v>24</v>
       </c>
       <c r="L6">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M6">
         <v>25</v>
       </c>
-      <c r="N6">
-        <v>0</v>
+      <c r="N6" t="s">
+        <v>22</v>
       </c>
       <c r="O6" t="s">
         <v>38</v>
@@ -1538,20 +1532,20 @@
       <c r="I7">
         <v>22347</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" t="s">
         <v>23</v>
       </c>
       <c r="K7" t="s">
         <v>24</v>
       </c>
       <c r="L7">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="M7">
         <v>45</v>
       </c>
-      <c r="N7">
-        <v>0</v>
+      <c r="N7" t="s">
+        <v>22</v>
       </c>
       <c r="O7" t="s">
         <v>42</v>
@@ -1588,20 +1582,20 @@
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" t="s">
         <v>23</v>
       </c>
       <c r="K8" t="s">
         <v>24</v>
       </c>
       <c r="L8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M8">
         <v>2</v>
       </c>
-      <c r="N8">
-        <v>0</v>
+      <c r="N8" t="s">
+        <v>22</v>
       </c>
       <c r="O8" t="s">
         <v>46</v>
@@ -1638,20 +1632,20 @@
       <c r="I9">
         <v>13</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" t="s">
         <v>23</v>
       </c>
       <c r="K9" t="s">
         <v>24</v>
       </c>
       <c r="L9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
-      <c r="N9">
-        <v>0</v>
+      <c r="N9" t="s">
+        <v>22</v>
       </c>
       <c r="O9" t="s">
         <v>49</v>
@@ -1688,22 +1682,22 @@
       <c r="I10">
         <v>2</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" t="s">
         <v>23</v>
       </c>
       <c r="K10" t="s">
         <v>24</v>
       </c>
       <c r="L10">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M10">
         <v>8</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
+      <c r="N10" t="s">
+        <v>22</v>
+      </c>
+      <c r="O10" s="2" t="s">
         <v>52</v>
       </c>
       <c r="P10" t="s">
@@ -1738,20 +1732,20 @@
       <c r="I11">
         <v>22347</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" t="s">
         <v>23</v>
       </c>
       <c r="K11" t="s">
         <v>24</v>
       </c>
       <c r="L11">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M11">
         <v>9</v>
       </c>
-      <c r="N11">
-        <v>0</v>
+      <c r="N11" t="s">
+        <v>22</v>
       </c>
       <c r="O11" t="s">
         <v>57</v>
@@ -1788,20 +1782,20 @@
       <c r="I12">
         <v>79621</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" t="s">
         <v>23</v>
       </c>
       <c r="K12" t="s">
         <v>24</v>
       </c>
       <c r="L12">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M12">
         <v>7</v>
       </c>
-      <c r="N12">
-        <v>0</v>
+      <c r="N12" t="s">
+        <v>22</v>
       </c>
       <c r="O12" t="s">
         <v>59</v>
@@ -1811,8 +1805,10 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="O10" r:id="rId1" display="http://data.zgsr.gov.cn:2003/info/6823.jspx"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>